--- a/KAMCHATKA_SUPPLIERS_KP.xlsx
+++ b/KAMCHATKA_SUPPLIERS_KP.xlsx
@@ -601,12 +601,13 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>+7 (351) 730-47-47 (пн-пт 8:30-17:30)</t>
+          <t>+7 (351) 730-47-47; +7 (922) 700-43-47
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>office@chsgs.ru; 166@ldtd.ru</t>
+          <t>office@chsgs.ru</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
@@ -631,7 +632,8 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 223-74-04</t>
+          <t>+7 (495) 223-74-04; 8-800-301-20-50
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -671,7 +673,8 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>8 800 350-91-13</t>
+          <t>8-800-350-91-13
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -701,7 +704,8 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>8 800 444-00-28 (служба продаж); приёмная 8 800 222-15-44</t>
+          <t>8-800-444-00-28 (продажи); 8-800-222-15-44
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -741,7 +745,8 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 937-89-68; Хабаровск +7 (4212) 72-97-83; Владивосток +7 (984) 159-21-64</t>
+          <t>+7 (495) 937-89-68; Хабаровск +7 (4212) 72-97-83; Владивосток +7 (984) 159-21-64
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -771,7 +776,8 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>+7 (8412) 35-07-97; +7 (495) 668-10-92</t>
+          <t>+7 (495) 668-10-92; +7 (8412) 35-07-97; +7 (812) 309-54-81
+[сайт promarm.com, 22.10.2026]</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -811,7 +817,8 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 792-57-57; 8-800-700-88-85</t>
+          <t>+7 (495) 792-57-57; 8-800-700-88-85
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -841,7 +848,8 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>8-800-201-58-67; +7 (48142) 2-88-09, 2-83-67</t>
+          <t>8-800-201-58-67; +7 (48142) 2-88-09, 2-83-67
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -881,7 +889,8 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>8 800 350-91-13</t>
+          <t>8-800-350-91-13
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -911,7 +920,8 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>8 800 444-00-28</t>
+          <t>8-800-444-00-28 (продажи); 8-800-222-15-44
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -951,7 +961,8 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 504-37-40; 8-800-777-95-16 (DN.ru)</t>
+          <t>+7 (495) 504-37-40; 8-800-777-95-16 (DN.ru)
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -981,7 +992,8 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>+7 (34766) 2-99-10</t>
+          <t>+7 (347) 662-99-10
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -1021,7 +1033,8 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 792-57-57; 8-800-700-88-85</t>
+          <t>+7 (495) 792-57-57; 8-800-700-88-85
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -1051,7 +1064,8 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 937-89-68; Хабаровск +7 (4212) 72-97-83</t>
+          <t>+7 (495) 937-89-68; Хабаровск +7 (4212) 72-97-83
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -1091,7 +1105,8 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 504-37-40; 8-800-777-95-16 (DN.ru)</t>
+          <t>+7 (495) 504-37-40; 8-800-777-95-16 (DN.ru)
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -1121,12 +1136,13 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>уточнить на semlmz.ru</t>
+          <t>нет на сайте
+[semlmz.ru — контакты на сайте не опубликованы; не звонить, искать через дилеров]</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>уточнить на semlmz.ru</t>
+          <t>нет на сайте</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -1161,7 +1177,8 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 937-89-68</t>
+          <t>+7 (495) 937-89-68
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -1191,12 +1208,13 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>+7 (991) 210-60-21</t>
+          <t>8-800-200-52-76; +7 (991) 210-60-21
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>reklama@pik-algrupp.ru (общий)</t>
+          <t>sales@pik-algrupp.ru</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -1231,7 +1249,8 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>+7 (351) 730-47-47</t>
+          <t>+7 (351) 730-47-47; +7 (922) 700-43-47
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -1261,7 +1280,8 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 937-89-68</t>
+          <t>+7 (495) 937-89-68
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -1301,7 +1321,8 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>+7 (351) 730-47-47</t>
+          <t>+7 (351) 730-47-47; +7 (922) 700-43-47
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -1331,7 +1352,8 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 458-55-97</t>
+          <t>+7 (812) 458-55-97
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -1371,7 +1393,8 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>+7 (499) 653-65-06</t>
+          <t>+7 (499) 653-65-06
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -1401,7 +1424,8 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>(8453) 75-48-28, 75-48-82</t>
+          <t>(8453) 75-48-28, 75-48-82
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -1441,7 +1465,8 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>+7 (4872) 72-47-16 (отдел реализации)</t>
+          <t>+7 (4872) 72-47-16 (отдел реализации)
+[сайт tulaprivod.ru не открылся 22.10 — проверить звонком]</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -1471,7 +1496,8 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>(8352) 305-148, 305-221</t>
+          <t>+7 (8352) 30-51-48; 30-52-21; Москва +7 (495) 735-42-44
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -1511,12 +1537,13 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 325-90-51; +7 (495) 666-33-01</t>
+          <t>+7 (812) 325-90-51; +7 (495) 666-33-01
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>info@rosma.spb.ru (уточнить)</t>
+          <t>info@rosma.spb.ru</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
@@ -1541,7 +1568,8 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 611-03-77</t>
+          <t>+7 (812) 611-03-77
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -1674,12 +1702,13 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>+7 (351) 730-47-47 (пн-пт 8:30-17:30)</t>
+          <t>+7 (351) 730-47-47; +7 (922) 700-43-47
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>office@chsgs.ru; 166@ldtd.ru</t>
+          <t>office@chsgs.ru</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
@@ -1724,7 +1753,8 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 223-74-04</t>
+          <t>+7 (495) 223-74-04; 8-800-301-20-50
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1774,7 +1804,8 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>8-800-444-74-74; +7 900 093-04-01</t>
+          <t>8-800-444-74-74; +7 (351) 246-02-10; +7 (351) 245-02-10
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1824,7 +1855,8 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>+7 (749) 527-55-88 (как в каталоге productcenter — уточнить номер)</t>
+          <t>+7 (495) 275-58-88
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1882,7 +1914,8 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>8 800 350-91-13</t>
+          <t>8-800-350-91-13
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -1932,7 +1965,8 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>8 800 444-00-28 (служба продаж); приёмная 8 800 222-15-44</t>
+          <t>8-800-444-00-28 (продажи); 8-800-222-15-44
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1982,12 +2016,13 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 411-77-57 (Москва); Алексин +7 (48753) 2-70-25, 2-61-13 (по armtorg.ru)</t>
+          <t>+7 (495) 411-77-57
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>office@aztpa.ru; ngskr@aztpa.ru (клиновые задвижки)</t>
+          <t>office@ogscomp.ru (указан на aztpa.ru)</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -2032,7 +2067,8 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>+7 (34766) 2-99-10; отдел продаж (34766) 2-11-74, 2-13-57 (по ibprom.ru)</t>
+          <t>+7 (347) 662-99-10
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -2090,7 +2126,8 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 937-89-68; Хабаровск +7 (4212) 72-97-83; Владивосток +7 (984) 159-21-64</t>
+          <t>+7 (495) 937-89-68; Хабаровск +7 (4212) 72-97-83; Владивосток +7 (984) 159-21-64
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -2140,7 +2177,8 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>+7 (8412) 35-07-97; +7 (495) 668-10-92</t>
+          <t>+7 (495) 668-10-92; +7 (8412) 35-07-97; +7 (812) 309-54-81
+[сайт promarm.com, 22.10.2026]</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -2190,7 +2228,8 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>(49241) 2-32-41, 2-42-26, 8-920-925-81-95 (отдел сбыта, по armtorg.ru)</t>
+          <t>(49241) 2-32-41, 2-42-26, 8-920-925-81-95 (отдел сбыта, по armtorg.ru)
+[сайт armagus.ru не открылся 22.10 — номер из armtorg.ru, проверить звонком]</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -2240,12 +2279,13 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>+7 (351) 307-71-09</t>
+          <t>+7 (351) 307-71-09
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>info@zaoutk.ru</t>
+          <t>info@aoutk.ru</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -2298,7 +2338,8 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 792-57-57; 8-800-700-88-85</t>
+          <t>+7 (495) 792-57-57; 8-800-700-88-85
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -2348,7 +2389,8 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>8-800-201-58-67; +7 (48142) 2-88-09, 2-83-67</t>
+          <t>8-800-201-58-67; +7 (48142) 2-88-09, 2-83-67
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -2398,7 +2440,8 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>(49241) 2-32-41, 2-42-26</t>
+          <t>(49241) 2-32-41, 2-42-26
+[сайт armagus.ru не открылся 22.10 — номер из armtorg.ru, проверить звонком]</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -2448,12 +2491,13 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>уточнить на сайте</t>
+          <t>8-800-700-77-85; +7 (495) 792-11-05
+[сайт teplo-sila.com, 22.10.2026]</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>уточнить на сайте</t>
+          <t>marketing@teplo-sila.com</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -2506,7 +2550,8 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>8 800 350-91-13</t>
+          <t>8-800-350-91-13
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -2556,7 +2601,8 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>8 800 444-00-28</t>
+          <t>8-800-444-00-28 (продажи); 8-800-222-15-44
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -2606,7 +2652,8 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 458-55-97; +7 (812) 334-92-39</t>
+          <t>+7 (812) 458-55-97; +7 (812) 334-92-39
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -2656,12 +2703,13 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 411-77-57</t>
+          <t>+7 (495) 411-77-57
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>office@aztpa.ru</t>
+          <t>office@ogscomp.ru (указан на aztpa.ru)</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -2714,7 +2762,8 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 504-37-40; 8-800-777-95-16 (DN.ru)</t>
+          <t>+7 (495) 504-37-40; 8-800-777-95-16 (DN.ru)
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -2764,7 +2813,8 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>+7 (34766) 2-99-10</t>
+          <t>+7 (347) 662-99-10
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -2814,7 +2864,8 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 458-55-97</t>
+          <t>+7 (812) 458-55-97
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -2864,7 +2915,8 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>через дилеров</t>
+          <t>через дилеров
+[только через дилеров (dn.ru)]</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -2922,7 +2974,8 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 792-57-57; 8-800-700-88-85</t>
+          <t>+7 (495) 792-57-57; 8-800-700-88-85
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -2972,7 +3025,8 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 937-89-68; Хабаровск +7 (4212) 72-97-83</t>
+          <t>+7 (495) 937-89-68; Хабаровск +7 (4212) 72-97-83
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -3022,7 +3076,8 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 458-55-97</t>
+          <t>+7 (812) 458-55-97
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -3072,7 +3127,8 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>(49241) 2-32-41, 2-42-26</t>
+          <t>(49241) 2-32-41, 2-42-26
+[сайт armagus.ru не открылся 22.10 — номер из armtorg.ru, проверить звонком]</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -3130,7 +3186,8 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 504-37-40; 8-800-777-95-16 (DN.ru)</t>
+          <t>+7 (495) 504-37-40; 8-800-777-95-16 (DN.ru)
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -3180,12 +3237,13 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>уточнить на semlmz.ru</t>
+          <t>нет на сайте
+[semlmz.ru — контакты на сайте не опубликованы; не звонить, искать через дилеров]</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>уточнить на semlmz.ru</t>
+          <t>нет на сайте</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
@@ -3230,7 +3288,8 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>уточнить</t>
+          <t>уточнить
+[не найден — не использовать]</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -3280,7 +3339,8 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>8 (495) 925-51-64</t>
+          <t>8 (495) 925-51-64
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -3338,7 +3398,8 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 937-89-68</t>
+          <t>+7 (495) 937-89-68
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -3388,12 +3449,13 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>+7 (991) 210-60-21</t>
+          <t>8-800-200-52-76; +7 (991) 210-60-21
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>reklama@pik-algrupp.ru (общий)</t>
+          <t>sales@pik-algrupp.ru</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -3438,7 +3500,8 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>+7 (34766) 2-99-10</t>
+          <t>+7 (347) 662-99-10
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -3488,7 +3551,8 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>уточнить</t>
+          <t>уточнить
+[не найден — не использовать]</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -3546,7 +3610,8 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>+7 (351) 730-47-47</t>
+          <t>+7 (351) 730-47-47; +7 (922) 700-43-47
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -3596,7 +3661,8 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 937-89-68</t>
+          <t>+7 (495) 937-89-68
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -3646,7 +3712,8 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 223-74-04</t>
+          <t>+7 (495) 223-74-04; 8-800-301-20-50
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -3696,7 +3763,8 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>через дилеров</t>
+          <t>через дилеров
+[только через дилеров (dn.ru)]</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -3754,7 +3822,8 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>+7 (351) 730-47-47</t>
+          <t>+7 (351) 730-47-47; +7 (922) 700-43-47
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -3804,7 +3873,8 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 458-55-97</t>
+          <t>+7 (812) 458-55-97
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -3854,7 +3924,8 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 611-03-77; 8-800-775-74-84</t>
+          <t>+7 (812) 611-03-77; 8-800-775-74-84
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -3912,7 +3983,8 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>+7 (499) 653-65-06</t>
+          <t>+7 (499) 653-65-06
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -3962,7 +4034,8 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>(8453) 75-48-28, 75-48-82</t>
+          <t>(8453) 75-48-28, 75-48-82
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -4012,7 +4085,8 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>уточнить</t>
+          <t>уточнить
+[консультация, не поставщик]</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
@@ -4070,7 +4144,8 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>+7 (4872) 72-47-16 (отдел реализации)</t>
+          <t>+7 (4872) 72-47-16 (отдел реализации)
+[сайт tulaprivod.ru не открылся 22.10 — проверить звонком]</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -4120,7 +4195,8 @@
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>(8352) 305-148, 305-221</t>
+          <t>+7 (8352) 30-51-48; 30-52-21; Москва +7 (495) 735-42-44
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -4170,7 +4246,8 @@
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>(49241) 2-32-41</t>
+          <t>(49241) 2-32-41
+[сайт armagus.ru не открылся 22.10 — номер из armtorg.ru, проверить звонком]</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -4228,12 +4305,13 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 325-90-51; +7 (495) 666-33-01</t>
+          <t>+7 (812) 325-90-51; +7 (495) 666-33-01
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>info@rosma.spb.ru (уточнить)</t>
+          <t>info@rosma.spb.ru</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -4278,7 +4356,8 @@
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 611-03-77</t>
+          <t>+7 (812) 611-03-77
+[сайт, 22.10.2026]</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -4328,7 +4407,8 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>через дилеров</t>
+          <t>через дилеров
+[только через дилеров (dn.ru)]</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
